--- a/DOSSIES_MULTIFORMATO/SUHAB/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SUHAB/dossie.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020NE01061</t>
+          <t>2020NE01048</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3184.4</v>
+        <v>40662.12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -655,14 +655,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 00994, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO, CONFORME DECRETO Nº 43.042, DE 18/11/2020.</t>
+          <t>ANULAÇÃO DO SALDO PARCIAL DA NE 00662, CONFORME DECRETO Nº 43.042, DE 18/11/2020.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020NE01051</t>
+          <t>2020NE01052</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2360</v>
+        <v>24269.02</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -681,14 +681,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 0027, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO, CONFORME DECRETO Nº 43.042, DE 18/11/2020.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 00028, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO, CONFORME DECRETO Nº 43.042, DE 18/11/2020.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020NE01052</t>
+          <t>2020NE01051</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24269.02</v>
+        <v>2360</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -707,14 +707,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 00028, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO, CONFORME DECRETO Nº 43.042, DE 18/11/2020.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 0027, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO, CONFORME DECRETO Nº 43.042, DE 18/11/2020.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020NE01048</t>
+          <t>2020NE01061</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40662.12</v>
+        <v>3184.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -733,21 +733,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO PARCIAL DA NE 00662, CONFORME DECRETO Nº 43.042, DE 18/11/2020.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 00994, EM VIRTUDE DO ENCERRAMENTO DO EXERCÍCIO, CONFORME DECRETO Nº 43.042, DE 18/11/2020.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023NE00678</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>9/2022</t>
-        </is>
-      </c>
+          <t>2023NE0000678</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>31/10/2023</t>
@@ -763,17 +759,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023NE0000678</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>2023NE00678</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9/2022</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>31/10/2023</t>
@@ -789,14 +789,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
+          <t>Cobertura Financeira</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2018NE00753</t>
+          <t>2018NE00754</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5110.98</v>
+        <v>86918.46000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -815,14 +815,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº 176/2018, POR ENCERRAMENTO DO PRAZO DO 4º TERMO ADITIVO AO CONTRATO Nº 17/2013-SUHAB/PRODAM.</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº 180/2018, POR ENCERRAMENTO DO PRAZO DO 1º TERMO ADITIVO AO CONTRATO Nº 17/2016-SUHAB/PRODOM PROCESSAMENTO DE DADOS AMAZONAS SA.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2018NE00754</t>
+          <t>2018NE00753</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>86918.46000000001</v>
+        <v>5110.98</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº 180/2018, POR ENCERRAMENTO DO PRAZO DO 1º TERMO ADITIVO AO CONTRATO Nº 17/2016-SUHAB/PRODOM PROCESSAMENTO DE DADOS AMAZONAS SA.</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº 176/2018, POR ENCERRAMENTO DO PRAZO DO 4º TERMO ADITIVO AO CONTRATO Nº 17/2013-SUHAB/PRODAM.</t>
         </is>
       </c>
     </row>
@@ -851,11 +851,7 @@
           <t>2016NE01104</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>14/2014</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>31/10/2016</t>
@@ -881,7 +877,11 @@
           <t>2016NE01104</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>14/2014</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>31/10/2016</t>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025NE0000385</t>
+          <t>2025NE0000384</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3606.6</v>
+        <v>8354.040000000001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -987,19 +987,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Contratação de solução tecnológica para gestão de margem consignável em folha de pagamento referente às parcelas de financiamentos da casa própria de servidores ativos, aposentados e pensionistas de Ó</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025NE0000383</t>
+          <t>2025NE0000382</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10193.26</v>
+        <v>4744.06</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
+          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025NE0000382</t>
+          <t>2025NE0000383</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4744.06</v>
+        <v>10193.26</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
+          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025NE0000384</t>
+          <t>2025NE0000385</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8354.040000000001</v>
+        <v>3606.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
+          <t>Contratação de solução tecnológica para gestão de margem consignável em folha de pagamento referente às parcelas de financiamentos da casa própria de servidores ativos, aposentados e pensionistas de Ó</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025NE0000584</t>
+          <t>2025NE0000585</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17941.56</v>
+        <v>4744.06</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1283,19 +1283,19 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025NE0000585</t>
+          <t>2025NE0000584</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4744.06</v>
+        <v>17941.56</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1313,21 +1313,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2022NE0000589</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>9/2020</t>
-        </is>
-      </c>
+          <t>2022NE00589</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>30/11/2022</t>
@@ -1343,17 +1339,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO TERMO AO CONTRATO 009/2020 -SUHAB/PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A, PARA CONTINUIDADE DO SERVIÇO CIRCUITO DE TRANSMISSÃO DE DADOS E ACESSO GERENCIADO A REDE MUNDIAL, I</t>
+          <t>2º T.A Contrato 009/2020</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2022NE00589</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>2022NE0000589</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>9/2020</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>30/11/2022</t>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2º T.A Contrato 009/2020</t>
+          <t>2º TERMO ADITIVO AO TERMO AO CONTRATO 009/2020 -SUHAB/PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A, PARA CONTINUIDADE DO SERVIÇO CIRCUITO DE TRANSMISSÃO DE DADOS E ACESSO GERENCIADO A REDE MUNDIAL, I</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025NE0000480</t>
+          <t>2025NE0000482</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17941.56</v>
+        <v>8354.040000000001</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025NE0000482</t>
+          <t>2025NE0000480</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8354.040000000001</v>
+        <v>17941.56</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2016NE01325</t>
+          <t>2016NE01352</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2587.37</v>
+        <v>28.14</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1575,14 +1575,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO NE Nº 52 POR ENCERRAMENTO DE EXERCÍCIO,CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO/2016-SET/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO NE Nº 177 POR ENCERRAMENTO DO EXERCÍCIO,CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO/2016-SET/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2016NE01343</t>
+          <t>2016NE01334</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>44.25</v>
+        <v>17045.7</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1601,14 +1601,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO NE 99 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO DE 2016-SET/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO NE Nº 74 POR ENCERRAMENTO DE EXERCÍCIO,CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO/2016-SET/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2016NE01379</t>
+          <t>2016NE01354</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2045.28</v>
+        <v>4451.16</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO NE Nº 1104 POR ENCERRAMENTO DO EXERCÍCIO,CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO/2016-SET/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO NE 103 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO DE 2016-SET/SEFAZ.</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2016NE01354</t>
+          <t>2016NE01379</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4451.16</v>
+        <v>2045.28</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1679,14 +1679,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO NE 103 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO DE 2016-SET/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO NE Nº 1104 POR ENCERRAMENTO DO EXERCÍCIO,CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO/2016-SET/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2016NE01334</t>
+          <t>2016NE01343</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>17045.7</v>
+        <v>44.25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1705,14 +1705,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO NE Nº 74 POR ENCERRAMENTO DE EXERCÍCIO,CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO/2016-SET/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO NE 99 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO DE 2016-SET/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2016NE01352</t>
+          <t>2016NE01325</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>28.14</v>
+        <v>2587.37</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO NE Nº 177 POR ENCERRAMENTO DO EXERCÍCIO,CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO/2016-SET/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO NE Nº 52 POR ENCERRAMENTO DE EXERCÍCIO,CONFORME INSTRUÇÃO NORMATIVA Nº 01/2016, DE 14 DE DEZEMBRO/2016-SET/SEFAZ.</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2022NE0000164</t>
+          <t>2022NE0000165</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1787.87</v>
+        <v>1629</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1843,14 +1843,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE SALDO DA NE Nº 100 DE ACORDO COM O DECRETO Nº 5.829 DE 24/03/22</t>
+          <t>ANULAÇÃO DO SALDO DA NE 0083 DE ACORDO COM A LEI 5.829 DE 24/03/2022</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2022NE0000636</t>
+          <t>2022NE0000172</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3462.63</v>
+        <v>16.33</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1869,14 +1869,14 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SAADO DA NE 188 CONTRATO 10/2018 POR ENCERRAMENTO DO PRAZO DO CONTRATO</t>
+          <t>ANUIAÇAO DO SAIDO DA NE 86 POR DETERMINAÇAO DA IEI 5.829 DE 24 DE MARÇO DE 2022</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2022NE0000647</t>
+          <t>2022NE0000637</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11930.33</v>
+        <v>1522.76</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ANUIAÇAO DO SAIDO DA NE 471 POR ENCERRAMENTO DO EXERCICIO CONFORME DECRETO 46.621 DE 11/11/2022</t>
+          <t>ANUIAÇAO DO SAADO DA NE 491 POR DETERMINAÇAO DO DECRETO 46.621 DE 11/11/2022</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2022NE0000637</t>
+          <t>2022NE0000647</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1522.76</v>
+        <v>11930.33</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1947,14 +1947,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ANUIAÇAO DO SAADO DA NE 491 POR DETERMINAÇAO DO DECRETO 46.621 DE 11/11/2022</t>
+          <t>ANUIAÇAO DO SAIDO DA NE 471 POR ENCERRAMENTO DO EXERCICIO CONFORME DECRETO 46.621 DE 11/11/2022</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2022NE0000172</t>
+          <t>2022NE0000636</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16.33</v>
+        <v>3462.63</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1973,14 +1973,14 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ANUIAÇAO DO SAIDO DA NE 86 POR DETERMINAÇAO DA IEI 5.829 DE 24 DE MARÇO DE 2022</t>
+          <t>ANULAÇÃO DO SAADO DA NE 188 CONTRATO 10/2018 POR ENCERRAMENTO DO PRAZO DO CONTRATO</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2022NE0000165</t>
+          <t>2022NE0000164</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1629</v>
+        <v>1787.87</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 0083 DE ACORDO COM A LEI 5.829 DE 24/03/2022</t>
+          <t>ANULAÇÃO DE SALDO DA NE Nº 100 DE ACORDO COM O DECRETO Nº 5.829 DE 24/03/22</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2017NE00798</t>
+          <t>2017NE00803</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>225119.02</v>
+        <v>128.84</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2051,14 +2051,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 18 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº 17 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2017NE00806</t>
+          <t>2017NE00820</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4944.85</v>
+        <v>0.55</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2077,14 +2077,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO NE 27 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO NE 095 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2017NE00832</t>
+          <t>2017NE00796</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3.27</v>
+        <v>29065.05</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO NE 266 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 09 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2017NE00796</t>
+          <t>2017NE00832</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>29065.05</v>
+        <v>3.27</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2155,14 +2155,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 09 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO NE 266 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2017NE00820</t>
+          <t>2017NE00806</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.55</v>
+        <v>4944.85</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2181,14 +2181,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO NE 095 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO NE 27 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2017NE00803</t>
+          <t>2017NE00798</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>128.84</v>
+        <v>225119.02</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº 17 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 18 POR ENCERRAMENTO DO EXERCÍCIO, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ.</t>
         </is>
       </c>
     </row>
@@ -2244,12 +2244,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2016NE01152</t>
+          <t>2016NE01166</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>23/2016</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1300.47</v>
+        <v>6614.68</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2267,19 +2267,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>COMPLEMENTO DO SALDO 5º TERMO ADITIVO AO CONTRATO Nº 04/2011-FEH/SUHAB, COM A EMPRESA PRODAM, REFERENTE AOS SERVIÇOS DE INFORMÁTICA PARA PROCESSAMENTO MENSAL DO SISTEMA CADASTRO E FOLHA DE PAGAMENTO D</t>
+          <t xml:space="preserve">TERMO DE CONTRATO Nº 023/2016-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE SERVIÇOS DE INFORMÁTICA, REFERENTE A PROCESSAMENTO DE CADASTRO DE FOLHA DE PAGAMENTO DE PESSOAL-SISTEMA CFPP. </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2016NE01166</t>
+          <t>2016NE01152</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>23/2016</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6614.68</v>
+        <v>1300.47</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERMO DE CONTRATO Nº 023/2016-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE SERVIÇOS DE INFORMÁTICA, REFERENTE A PROCESSAMENTO DE CADASTRO DE FOLHA DE PAGAMENTO DE PESSOAL-SISTEMA CFPP. </t>
+          <t>COMPLEMENTO DO SALDO 5º TERMO ADITIVO AO CONTRATO Nº 04/2011-FEH/SUHAB, COM A EMPRESA PRODAM, REFERENTE AOS SERVIÇOS DE INFORMÁTICA PARA PROCESSAMENTO MENSAL DO SISTEMA CADASTRO E FOLHA DE PAGAMENTO D</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2021NE0000389</t>
+          <t>2021NE0000387</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23/2016</t>
+          <t>28/2017</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>25129.32</v>
+        <v>8167.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SALDO DO 4º TERMO ADITIVO AO CONTRATO Nº 023/2016 -SUHAB/PRODAM , PELO PRAZO DE 12(DOZE) MESES, REF. A CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA SERVIÇOS DE EXECUÇÃO DO SISTEMA DE FOLHA DE PAGAMENTO D</t>
+          <t>SALDO DO 3º TERMO ADITIVO AO CONTRATO Nº 028/2017 SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A PELO PRAZO DE 12(DOZE) MESES, PARA CONTINUIDADE DOS SERVIÇOS DE FIREWALL, COMPREENDENDO A PRESTAÇÃO D</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2021NE0000387</t>
+          <t>2021NE0000389</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>28/2017</t>
+          <t>23/2016</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>8167.4</v>
+        <v>25129.32</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2417,14 +2417,14 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SALDO DO 3º TERMO ADITIVO AO CONTRATO Nº 028/2017 SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A PELO PRAZO DE 12(DOZE) MESES, PARA CONTINUIDADE DOS SERVIÇOS DE FIREWALL, COMPREENDENDO A PRESTAÇÃO D</t>
+          <t>SALDO DO 4º TERMO ADITIVO AO CONTRATO Nº 023/2016 -SUHAB/PRODAM , PELO PRAZO DE 12(DOZE) MESES, REF. A CONTRATAÇÃO DE EMPRESA ESPECIALIZADA PARA SERVIÇOS DE EXECUÇÃO DO SISTEMA DE FOLHA DE PAGAMENTO D</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2024NE0000775</t>
+          <t>2024NE0000769</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>28268.12</v>
+        <v>2163.96</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO PARCIAL DA NE Nº 57 DEVIDO ENCERRAMENTO DE EXERCÍCIO CONFORME DECRETO Nº 50.522 DE 22 DE OUTUBRO DE 2024.</t>
+          <t>ANULAÇÃO DO SALDO TOTAL DA NE Nº 101 DEVIDO ENCERRAMENTO DE EXERCÍCIO CONFORME DECRETO Nº 50.522 DE 22 DE OUTUBRO DE 2024.</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2024NE0000769</t>
+          <t>2024NE0000775</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2163.96</v>
+        <v>28268.12</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2495,14 +2495,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO TOTAL DA NE Nº 101 DEVIDO ENCERRAMENTO DE EXERCÍCIO CONFORME DECRETO Nº 50.522 DE 22 DE OUTUBRO DE 2024.</t>
+          <t>ANULAÇÃO DO SALDO PARCIAL DA NE Nº 57 DEVIDO ENCERRAMENTO DE EXERCÍCIO CONFORME DECRETO Nº 50.522 DE 22 DE OUTUBRO DE 2024.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2019NE00728</t>
+          <t>2019NE00740</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>77382.19</v>
+        <v>3.54</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2521,14 +2521,14 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº50/2019 POR ENCERRAMENTO DO PRAZO DO 2º TERMO ADITIVO AO CONTRATO Nº17/2016</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº191/2019 POR ENCERRAMENTO DO EXERCÍCIO CONFORME DECRETO Nº 41.554 DE 26 DE NOVEMBRO DE 2019</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2019NE00724</t>
+          <t>2019NE00750</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10024.1</v>
+        <v>1040</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2547,14 +2547,14 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº32/2019 POR ACERTO CONTÁBIL</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº432/2019 POR ENCERRAMENTO DO EXERCÍCIO CONFORME DECRETO Nº 41.554 DE 26 DE NOVEMBRO DE 2019</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2019NE00742</t>
+          <t>2019NE00748</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>51643.08</v>
+        <v>181.46</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº285/2019 POR ENCERRAMENTO DO EXERCÍCIO CONFORME DECRETO Nº 41.554 DE 26 DE NOVEMBRO DE 2019</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº412/2019 POR ENCERRAMENTO DO EXERCÍCIO CONFORME DECRETO Nº 41.554 DE 26 DE NOVEMBRO DE 2019</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2019NE00748</t>
+          <t>2019NE00742</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>181.46</v>
+        <v>51643.08</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2625,14 +2625,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº412/2019 POR ENCERRAMENTO DO EXERCÍCIO CONFORME DECRETO Nº 41.554 DE 26 DE NOVEMBRO DE 2019</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº285/2019 POR ENCERRAMENTO DO EXERCÍCIO CONFORME DECRETO Nº 41.554 DE 26 DE NOVEMBRO DE 2019</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2019NE00750</t>
+          <t>2019NE00724</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1040</v>
+        <v>10024.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2651,14 +2651,14 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº432/2019 POR ENCERRAMENTO DO EXERCÍCIO CONFORME DECRETO Nº 41.554 DE 26 DE NOVEMBRO DE 2019</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº32/2019 POR ACERTO CONTÁBIL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2019NE00740</t>
+          <t>2019NE00728</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3.54</v>
+        <v>77382.19</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2677,14 +2677,14 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº191/2019 POR ENCERRAMENTO DO EXERCÍCIO CONFORME DECRETO Nº 41.554 DE 26 DE NOVEMBRO DE 2019</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº50/2019 POR ENCERRAMENTO DO PRAZO DO 2º TERMO ADITIVO AO CONTRATO Nº17/2016</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2018NE00923</t>
+          <t>2018NE00938</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>100000</v>
+        <v>1040</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2703,14 +2703,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA Nº 390, POR ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO PARCIAL DA Nº 629, POR ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2018NE00948</t>
+          <t>2018NE00929</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5786.94</v>
+        <v>46.86</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE Nº 847, POR ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº 557, POR ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2018NE00929</t>
+          <t>2018NE00948</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>46.86</v>
+        <v>5786.94</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2781,14 +2781,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº 557, POR ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO PARCIAL DA NE Nº 847, POR ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2018NE00938</t>
+          <t>2018NE00923</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1040</v>
+        <v>100000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2807,19 +2807,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA Nº 629, POR ENCERRAMENTO DO EXERCÍCIO.</t>
+          <t>ANULAÇÃO PARCIAL DA Nº 390, POR ENCERRAMENTO DO EXERCÍCIO.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2024NE0000664</t>
+          <t>2024NE0000665</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>9567.540000000001</v>
+        <v>4177.02</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2837,19 +2837,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2024NE0000662</t>
+          <t>2024NE0000663</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12406.55</v>
+        <v>4452.84</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2867,19 +2867,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2024NE0000663</t>
+          <t>2024NE0000662</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4452.84</v>
+        <v>12406.55</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2897,19 +2897,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2024NE0000665</t>
+          <t>2024NE0000664</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4177.02</v>
+        <v>9567.540000000001</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
+          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
         </is>
       </c>
     </row>
@@ -2960,10 +2960,14 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2022NE0000471</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>2022NE00471</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>7/2022</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>27/09/2022</t>
@@ -2979,21 +2983,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO Nº 007/2022-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A PARA PRESTAÇÃO DE SERVIÇO DE IMPRESSÃO DE DOCUMENTOS E ENVELOPAMENTO DOS BOLETOS DE COBRANÇA DOS FINANCIAMENTOS IMOBILIÁR</t>
+          <t>Cobertura Financeira Contrato 007/2022</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2022NE00471</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>7/2022</t>
-        </is>
-      </c>
+          <t>2022NE0000471</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
           <t>27/09/2022</t>
@@ -3009,14 +3009,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cobertura Financeira Contrato 007/2022</t>
+          <t>TERMO DE CONTRATO Nº 007/2022-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A PARA PRESTAÇÃO DE SERVIÇO DE IMPRESSÃO DE DOCUMENTOS E ENVELOPAMENTO DOS BOLETOS DE COBRANÇA DOS FINANCIAMENTOS IMOBILIÁR</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2018NE00300</t>
+          <t>2018NE00296</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3039,14 +3039,14 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SERVIÇOS REALIZADOS NO MÊS DE AGOSTO/17 ,CORRESPONDENTE A UM DOS MÓDULOS PREVISTO NO CONTRATO 17/2016,REFERENTE A LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO.</t>
+          <t xml:space="preserve">RECONHECIMENTO DE DIVIDA Nº 17,REFERENTE A SERVIÇOS REALIZADOS NO MÊS DE DEZEMBRO/2017,CORRESPONDENTE A UM DOS MODULOS PREVISTO NO CONTRATO 17/2016,REFERENTE A LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO </t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2018NE00298</t>
+          <t>2018NE00299</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SERVIÇOS REALIZADOS NO MÊS DE SETEMBRO/2017,CORRESPONDENTE A UM DOS MODULOS PREVISTO NO CONTRATO 17/2016,REFERENTE A LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO .SOCIO/HABITACIONAL</t>
+          <t>RECONHECIMENTO DE DIVIDA Nº 16, REFERENTE A SERVIÇOS REALIZADOS NO MÊS DE NOVEMBRO/2017 - NOTA FISCAL Nº 1242, CORRESPONDENTE A UM DOS MÓDULOS PREVISTO NO CONTRATO 17/2016,REFERENTE A LICENÇA DE USO D</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2018NE00299</t>
+          <t>2018NE00298</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3129,14 +3129,14 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DE DIVIDA Nº 16, REFERENTE A SERVIÇOS REALIZADOS NO MÊS DE NOVEMBRO/2017 - NOTA FISCAL Nº 1242, CORRESPONDENTE A UM DOS MÓDULOS PREVISTO NO CONTRATO 17/2016,REFERENTE A LICENÇA DE USO D</t>
+          <t>SERVIÇOS REALIZADOS NO MÊS DE SETEMBRO/2017,CORRESPONDENTE A UM DOS MODULOS PREVISTO NO CONTRATO 17/2016,REFERENTE A LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO .SOCIO/HABITACIONAL</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2018NE00296</t>
+          <t>2018NE00300</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">RECONHECIMENTO DE DIVIDA Nº 17,REFERENTE A SERVIÇOS REALIZADOS NO MÊS DE DEZEMBRO/2017,CORRESPONDENTE A UM DOS MODULOS PREVISTO NO CONTRATO 17/2016,REFERENTE A LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO </t>
+          <t>SERVIÇOS REALIZADOS NO MÊS DE AGOSTO/17 ,CORRESPONDENTE A UM DOS MÓDULOS PREVISTO NO CONTRATO 17/2016,REFERENTE A LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO.</t>
         </is>
       </c>
     </row>
@@ -3192,12 +3192,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2024NE0000530</t>
+          <t>2024NE0000533</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>10/2018</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>841.54</v>
+        <v>9567.540000000001</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3215,19 +3215,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
+          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2024NE0000531</t>
+          <t>2024NE0000534</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>17311.46</v>
+        <v>8012.7</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3282,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2024NE0000534</t>
+          <t>2024NE0000531</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8012.7</v>
+        <v>17311.46</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3305,19 +3305,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2024NE0000533</t>
+          <t>2024NE0000530</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>10/2018</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>9567.540000000001</v>
+        <v>841.54</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
         </is>
       </c>
     </row>
@@ -3372,14 +3372,10 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2016NE00585</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>10/2016</t>
-        </is>
-      </c>
+          <t>2016NE00584</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
           <t>26/04/2016</t>
@@ -3395,7 +3391,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO Nº 10/2016-SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS SA .CONTRATAÇÃO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO,COMPREENDENDO A DISPONIBILIDADE DE GESTOR DE CONTEÚDO WEB A ESSA S</t>
+          <t>ANULAÇÃO DA NE 582 POR ERRO NA MODALIDADE.</t>
         </is>
       </c>
     </row>
@@ -3432,10 +3428,14 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2016NE00584</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>2016NE00585</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>10/2016</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
           <t>26/04/2016</t>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 582 POR ERRO NA MODALIDADE.</t>
+          <t>TERMO DE CONTRATO Nº 10/2016-SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS SA .CONTRATAÇÃO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO,COMPREENDENDO A DISPONIBILIDADE DE GESTOR DE CONTEÚDO WEB A ESSA S</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025NE0000154</t>
+          <t>2025NE0000152</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10193.26</v>
+        <v>17941.56</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3541,19 +3541,19 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025NE0000155</t>
+          <t>2025NE0000153</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>8354.040000000001</v>
+        <v>4744.06</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
+          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
         </is>
       </c>
     </row>
@@ -3608,12 +3608,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025NE0000153</t>
+          <t>2025NE0000155</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4744.06</v>
+        <v>8354.040000000001</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3631,19 +3631,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025NE0000152</t>
+          <t>2025NE0000154</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>17941.56</v>
+        <v>10193.26</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3788,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2023NE0000005</t>
+          <t>2023NE0000086</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2090.14</v>
+        <v>57696.45</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3807,14 +3807,14 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SALDO 1º TERMO ADITIVO AO CONTRATO Nº 001/2021-SUHAB/PRODAM PROCESSMANTO DE DADOS AMAZONAS S/A, POR PERIODO DE 12(DOZE) MESES, PARA CONTINUIDADE DOS SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO</t>
+          <t>ANULAÇÃO NA NE Nº 08 MOTIVO DATA DE EMISSÃO INCORRETA</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2023NE0000008</t>
+          <t>2023NE0000009</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>57696.45</v>
+        <v>9016.5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SALDO DO 2º TERMO ADITIVO AO TERMO AO CONTRATO 009/2020 -SUHAB/PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A, PARA CONTINUIDADE DO SERVIÇO CIRCUITO DE TRANSMISSÃO DE DADOS E ACESSO GERENCIADO A REDE M</t>
+          <t>SALDO DO 4º TERMO ADITIVO AO CONTRATO Nº 010/20218-SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A E REAJUSTAMENTO DO VALOR GLOBAL COM AUMENTO DE 10,70% COM BASE NO IGPM ACUMULADO DO PERÍODO, PELO P</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2023NE0000009</t>
+          <t>2023NE0000008</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>9016.5</v>
+        <v>57696.45</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3885,14 +3885,14 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SALDO DO 4º TERMO ADITIVO AO CONTRATO Nº 010/20218-SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A E REAJUSTAMENTO DO VALOR GLOBAL COM AUMENTO DE 10,70% COM BASE NO IGPM ACUMULADO DO PERÍODO, PELO P</t>
+          <t>SALDO DO 2º TERMO ADITIVO AO TERMO AO CONTRATO 009/2020 -SUHAB/PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A, PARA CONTINUIDADE DO SERVIÇO CIRCUITO DE TRANSMISSÃO DE DADOS E ACESSO GERENCIADO A REDE M</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2023NE0000086</t>
+          <t>2023NE0000005</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>57696.45</v>
+        <v>2090.14</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3911,14 +3911,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ANULAÇÃO NA NE Nº 08 MOTIVO DATA DE EMISSÃO INCORRETA</t>
+          <t>SALDO 1º TERMO ADITIVO AO CONTRATO Nº 001/2021-SUHAB/PRODAM PROCESSMANTO DE DADOS AMAZONAS S/A, POR PERIODO DE 12(DOZE) MESES, PARA CONTINUIDADE DOS SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025NE0000659</t>
+          <t>2025NE0000653</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>5085.99</v>
+        <v>2704.95</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3937,14 +3937,14 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº 11 DEVIDO O ENCERRAMENTO DE EXERCÍCIO CONFORME DECRETO Nº 52.770 DE 21 DE OUTUBRO DE 2025</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº 15 DEVIDO O ENCERRAMENTO DE EXERCÍCIO CONFORME DECRETO Nº 52.770 DE 21 DE OUTUBRO DE 2025</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025NE0000653</t>
+          <t>2025NE0000659</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2704.95</v>
+        <v>5085.99</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3963,14 +3963,14 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº 15 DEVIDO O ENCERRAMENTO DE EXERCÍCIO CONFORME DECRETO Nº 52.770 DE 21 DE OUTUBRO DE 2025</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº 11 DEVIDO O ENCERRAMENTO DE EXERCÍCIO CONFORME DECRETO Nº 52.770 DE 21 DE OUTUBRO DE 2025</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2016NE00263</t>
+          <t>2016NE00262</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>905.6</v>
+        <v>636.76</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -3993,14 +3993,14 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: RD RECONHECIMENTO DE DESPESA DE EXERCÍCIOS ANTERIORES Nº 17 PARA PAGAMENTO DE SERVIÇOS DE CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL, CORRESPONDENTE AO CONTRATO Nº 004/2011-FEH</t>
+          <t>RECONHECIMENTO DA DIVIDA: RD RECONHECIMENTO DE DESPESA DE EXERCÍCIOS ANTERIORES Nº 05 PARA PAGAMENTO DE SERVIÇOS DE CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL, CORRESPONDENTE AO CONTRATO Nº 004/2011-FEH</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2016NE00261</t>
+          <t>2016NE00264</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>625.12</v>
+        <v>1238.5</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4023,14 +4023,14 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: RD RECONHECIMENTO DE DESPESA DE EXERCÍCIOS ANTERIORES Nº 14 PARA PAGAMENTO DE SERVIÇOS DE CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL, CORRESPONDENTE AO CONTRATO Nº 004/2011-FEH</t>
+          <t>RECONHECIMENTO DA DIVIDA: RD RECONHECIMENTO DE DESPESA DE EXERCÍCIOS ANTERIORES Nº 33 PARA PAGAMENTO DE SERVIÇOS DE CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL, CORRESPONDENTE AO CONTRATO Nº 004/2011-FEH</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2016NE00264</t>
+          <t>2016NE00261</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1238.5</v>
+        <v>625.12</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4053,14 +4053,14 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: RD RECONHECIMENTO DE DESPESA DE EXERCÍCIOS ANTERIORES Nº 33 PARA PAGAMENTO DE SERVIÇOS DE CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL, CORRESPONDENTE AO CONTRATO Nº 004/2011-FEH</t>
+          <t>RECONHECIMENTO DA DIVIDA: RD RECONHECIMENTO DE DESPESA DE EXERCÍCIOS ANTERIORES Nº 14 PARA PAGAMENTO DE SERVIÇOS DE CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL, CORRESPONDENTE AO CONTRATO Nº 004/2011-FEH</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2016NE00262</t>
+          <t>2016NE00263</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>636.76</v>
+        <v>905.6</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4083,19 +4083,19 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>RECONHECIMENTO DA DIVIDA: RD RECONHECIMENTO DE DESPESA DE EXERCÍCIOS ANTERIORES Nº 05 PARA PAGAMENTO DE SERVIÇOS DE CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL, CORRESPONDENTE AO CONTRATO Nº 004/2011-FEH</t>
+          <t>RECONHECIMENTO DA DIVIDA: RD RECONHECIMENTO DE DESPESA DE EXERCÍCIOS ANTERIORES Nº 17 PARA PAGAMENTO DE SERVIÇOS DE CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL, CORRESPONDENTE AO CONTRATO Nº 004/2011-FEH</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025NE0000236</t>
+          <t>2025NE0000233</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>8354.040000000001</v>
+        <v>17941.56</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4113,19 +4113,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025NE0000235</t>
+          <t>2025NE0000234</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10193.26</v>
+        <v>4744.06</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
+          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025NE0000234</t>
+          <t>2025NE0000235</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4744.06</v>
+        <v>10193.26</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4203,19 +4203,19 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
+          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025NE0000233</t>
+          <t>2025NE0000236</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>17941.56</v>
+        <v>8354.040000000001</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4233,14 +4233,14 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2015NE01373</t>
+          <t>2015NE01364</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5598.99</v>
+        <v>738.51</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2015NE01364</t>
+          <t>2015NE01373</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>738.51</v>
+        <v>5598.99</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4322,12 +4322,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2024NE0000177</t>
+          <t>2024NE0000175</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>8012.7</v>
+        <v>4452.84</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
+          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2024NE0000175</t>
+          <t>2024NE0000177</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>4452.84</v>
+        <v>8012.7</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4405,24 +4405,28 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2023NE0000393</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>2023NE0000395</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>9/2022</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr">
         <is>
           <t>19/07/2023</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>17370</v>
+        <v>16025.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4431,19 +4435,19 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Contratação da Empresa PRODAM – Processamento de Dados Amazonas S/A para prestação de serviço de Impressão de documentos e envelopamento dos Boletos de Cobrança dos Financiamentos Imobiliários desta S</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2023NE0000392</t>
+          <t>2023NE0000388</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>10/2018</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4452,7 +4456,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>33486.39</v>
+        <v>6251.44</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4461,19 +4465,19 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2023NE0000390</t>
+          <t>2023NE0000389</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4482,7 +4486,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>13358.52</v>
+        <v>62696.81</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4491,19 +4495,19 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2023NE0000389</t>
+          <t>2023NE0000390</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4512,7 +4516,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>62696.81</v>
+        <v>13358.52</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4521,19 +4525,19 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2023NE0000388</t>
+          <t>2023NE0000392</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>10/2018</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4542,7 +4546,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>6251.44</v>
+        <v>33486.39</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4551,28 +4555,24 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
+          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2023NE0000395</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>9/2022</t>
-        </is>
-      </c>
+          <t>2023NE0000393</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
           <t>19/07/2023</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>16025.4</v>
+        <v>17370</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance.</t>
+          <t>Contratação da Empresa PRODAM – Processamento de Dados Amazonas S/A para prestação de serviço de Impressão de documentos e envelopamento dos Boletos de Cobrança dos Financiamentos Imobiliários desta S</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2023NE0000247</t>
+          <t>2023NE0000248</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1803.3</v>
+        <v>11539.29</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4753,14 +4753,14 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2023NE0000248</t>
+          <t>2023NE0000247</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11539.29</v>
+        <v>1803.3</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4779,14 +4779,14 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2023NE0000236</t>
+          <t>2023NE0000242</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>4006.35</v>
+        <v>5790</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance.</t>
+          <t>Contratação da Empresa PRODAM – Processamento de Dados Amazonas S/A para prestação de serviço de Impressão de documentos e envelopamento dos Boletos de Cobrança dos Financiamentos Imobiliários desta S</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2023NE0000242</t>
+          <t>2023NE0000236</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>5790</v>
+        <v>4006.35</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4857,19 +4857,19 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Contratação da Empresa PRODAM – Processamento de Dados Amazonas S/A para prestação de serviço de Impressão de documentos e envelopamento dos Boletos de Cobrança dos Financiamentos Imobiliários desta S</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2021NE0000074</t>
+          <t>2021NE0000070</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4878,7 +4878,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>21030.32</v>
+        <v>6868.12</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4887,19 +4887,19 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFORÇO NE 00055 - prestação dos serviços de fornecimento de Circuito de Transmissão de Dados, possibilitando o acesso aos sistemas contratados residentes no Data Center do Estado, incluindo o Acesso </t>
+          <t xml:space="preserve">REFORÇO DA NE 00062 - prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, vídeos e </t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2021NE0000071</t>
+          <t>2021NE0000072</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>23/2016</t>
+          <t>28/2017</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>8376.440000000001</v>
+        <v>8167.4</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 00052 - serviços de execução de Sistemas PRODAM-RH para manter o cadastro dos servidores e folha de pagamento, para atender as necessidades desta SUHAB.</t>
+          <t>REFORÇO DA NE 00053 - prestação de serviços de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação com a disponibilidade de Appliance para ate</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2021NE0000072</t>
+          <t>2021NE0000071</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>28/2017</t>
+          <t>23/2016</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>8167.4</v>
+        <v>8376.440000000001</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -4977,19 +4977,19 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE 00053 - prestação de serviços de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação com a disponibilidade de Appliance para ate</t>
+          <t>REFORÇO DA NE 00052 - serviços de execução de Sistemas PRODAM-RH para manter o cadastro dos servidores e folha de pagamento, para atender as necessidades desta SUHAB.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2021NE0000070</t>
+          <t>2021NE0000074</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>6868.12</v>
+        <v>21030.32</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFORÇO DA NE 00062 - prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, vídeos e </t>
+          <t xml:space="preserve">REFORÇO NE 00055 - prestação dos serviços de fornecimento de Circuito de Transmissão de Dados, possibilitando o acesso aos sistemas contratados residentes no Data Center do Estado, incluindo o Acesso </t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2022NE00491</t>
+          <t>2022NE0000491</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5187,14 +5187,14 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Serviço de Desconto em consignação das prestações do financiamento da casa própria.</t>
+          <t>4º TERMO ADITIVO AO CONTRATO Nº 010/20218-SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A E REAJUSTAMENTO DO VALOR GLOBAL COM AUMENTO DE 10,70% COM BASE NO IGPM ACUMULADO DO PERÍODO, PELO PRAZO DE 1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2022NE0000491</t>
+          <t>2022NE00491</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>4º TERMO ADITIVO AO CONTRATO Nº 010/20218-SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A E REAJUSTAMENTO DO VALOR GLOBAL COM AUMENTO DE 10,70% COM BASE NO IGPM ACUMULADO DO PERÍODO, PELO PRAZO DE 1</t>
+          <t>Serviço de Desconto em consignação das prestações do financiamento da casa própria.</t>
         </is>
       </c>
     </row>
@@ -5310,12 +5310,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2022NE0000187</t>
+          <t>2022NE0000188</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>10/2018</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>89617.07000000001</v>
+        <v>10539.63</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5333,24 +5333,28 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SALDO DO 1º TERMO ADITIVO AO TERMO AO CONTRATO 009/2020 -SUHAB/PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A, PARA CONTINUIDADE DO SERVIÇO CIRCUITO DE TRANSMISSÃO DE DADOS E ACESSO GERENCIADO A REDE M</t>
+          <t>3º TERMO ADITIVO AO CONTRATO Nº 010/20218-SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A E REAJUSTAMENTO DO VALOR GLOBAL COM AUMENTO DE 35,75% COM BASE NO IGPM ACUMULADO DO PERÍODO, PELO PRAZO DE 1</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2022NE0000186</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr"/>
+          <t>2022NE0000189</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1/2022</t>
+        </is>
+      </c>
       <c r="C168" t="inlineStr">
         <is>
           <t>13/05/2022</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>21798.8</v>
+        <v>53891.52</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5359,28 +5363,24 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SALDO DO 4º TERMO ADITIVO AO CONTRATO Nº 28/2017 - SUHAB/PRODAM PROCESSAMENTOS DE DADOS AMAZONAS S/A, PELO PRAZO DE 12(DOZE) MESES, REAJUSTE DO VALOR GLOBAL COM AUMENTO DE 6,76% COM BASE NO IPCA, PARA</t>
+          <t>TERMO DE CONTRATO Nº 001/2022-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, POR 12(DOZE) MESES, PARA FORNECIMENTO DE SERVIÇO DE EXECUÇÃO DE SISTEMAS PRODAM-RH PARA CONTROLE DE CADASTRO PESSOAL (SE</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2022NE0000189</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>1/2022</t>
-        </is>
-      </c>
+          <t>2022NE0000186</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
           <t>13/05/2022</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>53891.52</v>
+        <v>21798.8</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5389,19 +5389,19 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO Nº 001/2022-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, POR 12(DOZE) MESES, PARA FORNECIMENTO DE SERVIÇO DE EXECUÇÃO DE SISTEMAS PRODAM-RH PARA CONTROLE DE CADASTRO PESSOAL (SE</t>
+          <t>SALDO DO 4º TERMO ADITIVO AO CONTRATO Nº 28/2017 - SUHAB/PRODAM PROCESSAMENTOS DE DADOS AMAZONAS S/A, PELO PRAZO DE 12(DOZE) MESES, REAJUSTE DO VALOR GLOBAL COM AUMENTO DE 6,76% COM BASE NO IPCA, PARA</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2022NE0000188</t>
+          <t>2022NE0000187</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>10/2018</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>10539.63</v>
+        <v>89617.07000000001</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5419,19 +5419,19 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>3º TERMO ADITIVO AO CONTRATO Nº 010/20218-SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A E REAJUSTAMENTO DO VALOR GLOBAL COM AUMENTO DE 35,75% COM BASE NO IGPM ACUMULADO DO PERÍODO, PELO PRAZO DE 1</t>
+          <t>SALDO DO 1º TERMO ADITIVO AO TERMO AO CONTRATO 009/2020 -SUHAB/PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A, PARA CONTINUIDADE DO SERVIÇO CIRCUITO DE TRANSMISSÃO DE DADOS E ACESSO GERENCIADO A REDE M</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2018NE00176</t>
+          <t>2018NE00179</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>17/2013</t>
+          <t>1/2015</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>7754.73</v>
+        <v>100241.05</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5449,19 +5449,19 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SALDO DO 4º TERMO ADITIVO AO CONTRATO Nº 17/2013 COM PRORROGAÇÃO DE PRAZO E REAJUSTE NO PERCENTUAL DE 3,36 % (TRÊS VÍRGULA TRINTA E SEIS POR CENTO) COM BASE NO IGPM REFERENTE A CONTRATAÇÃO DOS SERVIÇO</t>
+          <t>4º TERMO ADITIVO AO TERMO DE CONTRATO 001/2015-SUHAB/PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A,REFERENTE A PRORROGAÇÃO DO PRAZO PELO PERÍODO DE 12(DOZE)MESES , CORRESPONDENTE A CONTRATAÇÃO DOS SER</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2018NE00181</t>
+          <t>2018NE00180</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>23/2016</t>
+          <t>17/2016</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>36029.84</v>
+        <v>293308.58</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5479,19 +5479,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>SALDO DO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 023/2016-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A PELO PERIODO DE 12(DOZE) MESES,PARA CONTINUIDADE DOS SERVIÇOS.</t>
+          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 017/2016-SUHAB/PRODAM - PROCESSAMENTO DE DADOS AMAZONAS S/A, PRORROGAÇÃO DE PRAZO E REAJUSTE NO PERCENTUAL DE 4,86% COM BASE NO IGPM ACUMULADO DO PERÍODO, REFE</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2018NE00178</t>
+          <t>2018NE00177</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>28/2017</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>3147.13</v>
+        <v>24535.25</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5509,19 +5509,19 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 010/2016-SUHAB/PRODAM - PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE A PRORROGAÇÃO E REAJUSTAMENTO NO PERCENTUAL 6,66%, COM BASE NO IGPM ACUMULADO NO PERÍODO,</t>
+          <t>SALDO DO TERMO DE CONTRATO Nº 028/2017-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE A CONTRATAÇÃO DOS SERVIÇOS DE FIREWALL, COMPREENDENDO A PRESTAÇÃO DE</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2018NE00177</t>
+          <t>2018NE00178</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>28/2017</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>24535.25</v>
+        <v>3147.13</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5539,19 +5539,19 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>SALDO DO TERMO DE CONTRATO Nº 028/2017-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE A CONTRATAÇÃO DOS SERVIÇOS DE FIREWALL, COMPREENDENDO A PRESTAÇÃO DE</t>
+          <t>ALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 010/2016-SUHAB/PRODAM - PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE A PRORROGAÇÃO E REAJUSTAMENTO NO PERCENTUAL 6,66%, COM BASE NO IGPM ACUMULADO NO PERÍODO,</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2018NE00180</t>
+          <t>2018NE00181</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>17/2016</t>
+          <t>23/2016</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>293308.58</v>
+        <v>36029.84</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5569,19 +5569,19 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 017/2016-SUHAB/PRODAM - PROCESSAMENTO DE DADOS AMAZONAS S/A, PRORROGAÇÃO DE PRAZO E REAJUSTE NO PERCENTUAL DE 4,86% COM BASE NO IGPM ACUMULADO DO PERÍODO, REFE</t>
+          <t>SALDO DO PRIMEIRO TERMO ADITIVO AO CONTRATO Nº 023/2016-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A PELO PERIODO DE 12(DOZE) MESES,PARA CONTINUIDADE DOS SERVIÇOS.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2018NE00179</t>
+          <t>2018NE00176</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1/2015</t>
+          <t>17/2013</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>100241.05</v>
+        <v>7754.73</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>4º TERMO ADITIVO AO TERMO DE CONTRATO 001/2015-SUHAB/PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A,REFERENTE A PRORROGAÇÃO DO PRAZO PELO PERÍODO DE 12(DOZE)MESES , CORRESPONDENTE A CONTRATAÇÃO DOS SER</t>
+          <t>SALDO DO 4º TERMO ADITIVO AO CONTRATO Nº 17/2013 COM PRORROGAÇÃO DE PRAZO E REAJUSTE NO PERCENTUAL DE 3,36 % (TRÊS VÍRGULA TRINTA E SEIS POR CENTO) COM BASE NO IGPM REFERENTE A CONTRATAÇÃO DOS SERVIÇO</t>
         </is>
       </c>
     </row>
@@ -5636,12 +5636,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2024NE0000370</t>
+          <t>2024NE0000372</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>10/2018</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>3606.6</v>
+        <v>4452.84</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5659,19 +5659,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
+          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2024NE0000371</t>
+          <t>2024NE0000373</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>17311.46</v>
+        <v>9567.540000000001</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2024NE0000373</t>
+          <t>2024NE0000371</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>9567.540000000001</v>
+        <v>17311.46</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5749,19 +5749,19 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2024NE0000372</t>
+          <t>2024NE0000370</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>10/2018</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4452.84</v>
+        <v>3606.6</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5779,19 +5779,19 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2023NE0000750</t>
+          <t>2023NE0000751</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>10/2018</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>4904.91</v>
+        <v>1803.3</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2023NE0000751</t>
+          <t>2023NE0000750</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>10/2018</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1803.3</v>
+        <v>4904.91</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5869,19 +5869,19 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2020NE00994</t>
+          <t>2020NE00993</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>17/2016</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3184.4</v>
+        <v>5257.58</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5899,19 +5899,19 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA ATRAVÉS DO 5º TERMO ADITIVO AO CONTRATO Nº 17/2016 -SUHAB, CELEBRADO ENTRE A SUPERINTENDÊNCIA ESTADUAL DE HABITAÇÃO E EMPRESA PROCESSAMENTO DE DADOS DO AMAZONAS S/A PA</t>
+          <t xml:space="preserve">CONTRATAÇÃO PARA A PRESTAÇÃO DOS SERVIÇOS DE FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS, POSSIBILITANDO O ACESSO AOS SISTEMAS CONTRATADOS RESIDENTES NO DATA CENTER DO ESTADO, INCLUINDO O ACESSO </t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2020NE00993</t>
+          <t>2020NE00994</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>17/2016</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>5257.58</v>
+        <v>3184.4</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5929,14 +5929,14 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO PARA A PRESTAÇÃO DOS SERVIÇOS DE FORNECIMENTO DE CIRCUITO DE TRANSMISSÃO DE DADOS, POSSIBILITANDO O ACESSO AOS SISTEMAS CONTRATADOS RESIDENTES NO DATA CENTER DO ESTADO, INCLUINDO O ACESSO </t>
+          <t>PRORROGAÇÃO DO PRAZO DE VIGÊNCIA ATRAVÉS DO 5º TERMO ADITIVO AO CONTRATO Nº 17/2016 -SUHAB, CELEBRADO ENTRE A SUPERINTENDÊNCIA ESTADUAL DE HABITAÇÃO E EMPRESA PROCESSAMENTO DE DADOS DO AMAZONAS S/A PA</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2015NE01004</t>
+          <t>2015NE10004</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5959,14 +5959,14 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO PARA PRESTAÇÃO DE SERVIÇO DE LOCAÇÃO DE EQUIPAMENTOS DE INFORMÁTICA. 3º TERMO ADITIVO AO CONTRATO Nº 08/2012 SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS SA REFERENTE LOCAÇÃO DE EQUIPAMEN</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2015NE10004</t>
+          <t>2015NE01004</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>CONTRATAÇÃO PARA PRESTAÇÃO DE SERVIÇO DE LOCAÇÃO DE EQUIPAMENTOS DE INFORMÁTICA. 3º TERMO ADITIVO AO CONTRATO Nº 08/2012 SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS SA REFERENTE LOCAÇÃO DE EQUIPAMEN</t>
         </is>
       </c>
     </row>
@@ -6176,10 +6176,14 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2018NE00846</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr"/>
+          <t>2018NE00845</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>23/2016</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>07/12/2018</t>
@@ -6195,7 +6199,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 845/2018 POR ERRO NA DESCRIÇÃO.</t>
+          <t>Contratação de empresa para prestaçãode serviços de sistema PRODAM-RH, para manter o cadstro dps servidores e folha de pagamentode pessoal, processar folhas de pagamento e fornecer relatórios para ate</t>
         </is>
       </c>
     </row>
@@ -6232,14 +6236,10 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2018NE00845</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>23/2016</t>
-        </is>
-      </c>
+          <t>2018NE00846</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr">
         <is>
           <t>07/12/2018</t>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestaçãode serviços de sistema PRODAM-RH, para manter o cadstro dps servidores e folha de pagamentode pessoal, processar folhas de pagamento e fornecer relatórios para ate</t>
+          <t>ANULAÇÃO DA NE 845/2018 POR ERRO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2017NE00264</t>
+          <t>2017NE00266</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6348,7 +6348,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2017NE00266</t>
+          <t>2017NE00264</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6408,7 +6408,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2018NE00165</t>
+          <t>2018NE00162</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -6418,7 +6418,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>54603.41</v>
+        <v>3147.13</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6427,14 +6427,14 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 99 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 035 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2018NE00161</t>
+          <t>2018NE00169</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>36029.84</v>
+        <v>7754.73</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6453,14 +6453,14 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 033 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 062 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2018NE00164</t>
+          <t>2018NE00166</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>24535.25</v>
+        <v>0.05</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6479,14 +6479,14 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 064 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO DA NE N º 47 .</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2018NE00170</t>
+          <t>2018NE00163</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -6496,7 +6496,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>100241.05</v>
+        <v>238705.17</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6505,14 +6505,14 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 0107 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 058 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2018NE00163</t>
+          <t>2018NE00170</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>238705.17</v>
+        <v>100241.05</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6531,14 +6531,14 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 058 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 0107 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2018NE00166</t>
+          <t>2018NE00164</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.05</v>
+        <v>24535.25</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -6557,14 +6557,14 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE N º 47 .</t>
+          <t>ANULAÇÃO DO SALDO DA NE 064 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2018NE00169</t>
+          <t>2018NE00161</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>7754.73</v>
+        <v>36029.84</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6583,14 +6583,14 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 062 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
+          <t>ANULAÇÃO DO SALDO DA NE 033 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2018NE00162</t>
+          <t>2018NE00165</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>3147.13</v>
+        <v>54603.41</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6609,14 +6609,14 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE 035 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
+          <t>ANULAÇÃO DA NE 99 PARA TROCA DE NATUREZA DA DESPESA CONFORME ORIENTAÇÃO TÉCNICA Nº 12/2018-GINS/SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2023NE0000741</t>
+          <t>2023NE0000742</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>2704.95</v>
+        <v>2545.64</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº 19 DE ACORDO COM O DECRETO 48.346/2023 DE 26/10/2023</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº 14 DE ACORDO COM O DECRETO 48.346/2023 DE 26/10/2023</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2023NE0000742</t>
+          <t>2023NE0000741</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2545.64</v>
+        <v>2704.95</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DO SALDO DA NE Nº 14 DE ACORDO COM O DECRETO 48.346/2023 DE 26/10/2023</t>
+          <t>ANULAÇÃO DO SALDO DA NE Nº 19 DE ACORDO COM O DECRETO 48.346/2023 DE 26/10/2023</t>
         </is>
       </c>
     </row>
@@ -6724,14 +6724,10 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2016NE00598</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>25/2013</t>
-        </is>
-      </c>
+          <t>2016NE00597</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
           <t>06/05/2016</t>
@@ -6747,7 +6743,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SALDO DO TERMO DE CONTRATO Nº 25/2013 SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONA S/A, REFERENTE RECUPERAÇÃO E MANUTENÇÃO DA REDE DE COMPUTADORES, COMPREENDENDO A INSTALAÇÃO DE 458 PONTOS DE TELECOMUN</t>
+          <t>ANULAÇÃO DA NE Nº 596 POR ERRO NA REFERÊNCIA.</t>
         </is>
       </c>
     </row>
@@ -6784,10 +6780,14 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2016NE00597</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr"/>
+          <t>2016NE00598</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>25/2013</t>
+        </is>
+      </c>
       <c r="C218" t="inlineStr">
         <is>
           <t>06/05/2016</t>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE Nº 596 POR ERRO NA REFERÊNCIA.</t>
+          <t>SALDO DO TERMO DE CONTRATO Nº 25/2013 SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONA S/A, REFERENTE RECUPERAÇÃO E MANUTENÇÃO DA REDE DE COMPUTADORES, COMPREENDENDO A INSTALAÇÃO DE 458 PONTOS DE TELECOMUN</t>
         </is>
       </c>
     </row>
@@ -6930,12 +6930,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026NE0000019</t>
+          <t>2026NE0000018</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>7213.2</v>
+        <v>17202.64</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Contratação de solução tecnológica para gestão de margem consignável em folha de pagamento referente às parcelas de financiamentos da casa própria de servidores ativos, aposentados e pensionistas de Ó</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026NE0000018</t>
+          <t>2026NE0000019</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>17202.64</v>
+        <v>7213.2</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7013,19 +7013,19 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
+          <t>Contratação de solução tecnológica para gestão de margem consignável em folha de pagamento referente às parcelas de financiamentos da casa própria de servidores ativos, aposentados e pensionistas de Ó</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2015NE00132</t>
+          <t>2015NE00130</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>13/2009</t>
+          <t>17/2013</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>8220.040000000001</v>
+        <v>7372.4</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7043,19 +7043,19 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SALDO DO 7º TERMO ADITIVO AO CONTRATO Nº 13/2009 SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A REFERENTE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO O FORNECIMENTO DE UM LINK DEDICADOS DE</t>
+          <t>1º TERMO ADITIVO AO CONTRATO Nº 17/2013 SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS SA REFERENTE SERVIÇOS DE INFORMÁTICA PARA GERAÇÃO DE CONSIGNAÇÃO DO FINANCIAMENTO DA CASA PRÓPRIA ATRAVÉS DOS CÓDI</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2015NE00141</t>
+          <t>2015NE00101</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7064,7 +7064,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>27913.5</v>
+        <v>3901.41</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7073,19 +7073,19 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALDO D2º TERMO ADITIVO AO CONTRATO Nº 08/2012 SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS SA REFERENTE LOCAÇÃO DE EQUIPAMENTOS COMPREENDENDO INSTALAÇÃO, CONFIGURAÇÃO, MANUTENÇÃO E ADMINISTRAÇÃO DE </t>
+          <t>4º TERMO DE RERRATIFICAÇÃO AO CONTRATO Nº004/2011-FEH/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S.A MODIFICANDO A CLAUSULA VIGESIMA SEGUNDA.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2015NE00066</t>
+          <t>2015NE00065</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7094,7 +7094,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>3506.24</v>
+        <v>25581</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7110,12 +7110,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2015NE00065</t>
+          <t>2015NE00066</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>25581</v>
+        <v>3506.24</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7140,12 +7140,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2015NE00101</t>
+          <t>2015NE00141</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>3901.41</v>
+        <v>27913.5</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7163,19 +7163,19 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>4º TERMO DE RERRATIFICAÇÃO AO CONTRATO Nº004/2011-FEH/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S.A MODIFICANDO A CLAUSULA VIGESIMA SEGUNDA.</t>
+          <t xml:space="preserve">SALDO D2º TERMO ADITIVO AO CONTRATO Nº 08/2012 SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS SA REFERENTE LOCAÇÃO DE EQUIPAMENTOS COMPREENDENDO INSTALAÇÃO, CONFIGURAÇÃO, MANUTENÇÃO E ADMINISTRAÇÃO DE </t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2015NE00130</t>
+          <t>2015NE00132</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>17/2013</t>
+          <t>13/2009</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>7372.4</v>
+        <v>8220.040000000001</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO AO CONTRATO Nº 17/2013 SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS SA REFERENTE SERVIÇOS DE INFORMÁTICA PARA GERAÇÃO DE CONSIGNAÇÃO DO FINANCIAMENTO DA CASA PRÓPRIA ATRAVÉS DOS CÓDI</t>
+          <t>SALDO DO 7º TERMO ADITIVO AO CONTRATO Nº 13/2009 SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A REFERENTE SERVIÇOS TÉCNICOS EM TELECOMUNICAÇÕES, COMPREENDENDO O FORNECIMENTO DE UM LINK DEDICADOS DE</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2021NE0000055</t>
+          <t>2021NE0000052</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>23/2016</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>42060.64</v>
+        <v>16752.88</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7283,19 +7283,19 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação para a prestação dos serviços de fornecimento de Circuito de Transmissão de Dados, possibilitando o acesso aos sistemas contratados residentes no Data Center do Estado, incluindo o Acesso </t>
+          <t>Contratação dos serviços de execução de Sistemas PRODAM-RH para manter o cadastro dos servidores e folha de pagamento, para atender as necessidades desta SUHAB.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2021NE0000052</t>
+          <t>2021NE0000055</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>23/2016</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>16752.88</v>
+        <v>42060.64</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7313,19 +7313,19 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de execução de Sistemas PRODAM-RH para manter o cadastro dos servidores e folha de pagamento, para atender as necessidades desta SUHAB.</t>
+          <t xml:space="preserve">Contratação para a prestação dos serviços de fornecimento de Circuito de Transmissão de Dados, possibilitando o acesso aos sistemas contratados residentes no Data Center do Estado, incluindo o Acesso </t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2016NE00075</t>
+          <t>2016NE00103</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>14/2014</t>
+          <t>17/2013</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7334,7 +7334,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>25581</v>
+        <v>7674.66</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7343,19 +7343,19 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 014/2011- SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS ,REFERENTE A CONTRATAÇÃO DE SERVIÇOS DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOL</t>
+          <t xml:space="preserve">SALDO DO 2º TERMO ADITIVO AO CONTRATO Nº 17/2013 SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S.A, REFERENTE A CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DE SISTEMA, COMPREENDENDO GERAÇÃO DE CONSIGNAÇÃO DO </t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2016NE00099</t>
+          <t>2016NE00052</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>1/2015</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>8413.940000000001</v>
+        <v>7802.82</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -7373,19 +7373,19 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 01/2015 SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE SERVIÇOS DE REDE COMPREENDENDO DISPONIBILIDADE DE ACESSO A REDE DO GOVERNO, VIA CIRCUITO DE</t>
+          <t xml:space="preserve">SALDO DO 5º TERMO ADITIVO AO CONTRATO Nº 04/2011 - FEH/SUHAB - PRODAM S.A , REFERENTE AOS SERVIÇOS DE INFORMÁTICA PARA PROCESSAMENTO MENSAL DO SISTEMA CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL - CFPP. </t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2016NE00078</t>
+          <t>2016NE00057</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>9/2014</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>29471.11</v>
+        <v>3701.92</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -7403,19 +7403,19 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>SALDO DO 3º TERMO ADITIVO AO CONTRATO Nº 08/2012 SUHAB/ PRODAM, PROCESSAMENTOS DE DADOS AMAZONAS SA, REFERENTE A CONTRATAÇÃO DE SERVIÇOS DE LOTAÇÃO DE EQUIPAMENTOS, COMPREENDENDO A INSTALAÇÃO E CONFIG</t>
+          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO 09/2014 SUHAB/PRODAM PROCESSAMENTO DE DADOS DO AMAZONAS S.A, MANUTENÇÃO DE NOVA FUNCIONALIDADE NO SITE INSTITUCIONAL . VIGÊNCIA; 18/09/2015 A 18/09/2016 VALOR GLO</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2016NE00057</t>
+          <t>2016NE00078</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>9/2014</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>3701.92</v>
+        <v>29471.11</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -7433,19 +7433,19 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO 09/2014 SUHAB/PRODAM PROCESSAMENTO DE DADOS DO AMAZONAS S.A, MANUTENÇÃO DE NOVA FUNCIONALIDADE NO SITE INSTITUCIONAL . VIGÊNCIA; 18/09/2015 A 18/09/2016 VALOR GLO</t>
+          <t>SALDO DO 3º TERMO ADITIVO AO CONTRATO Nº 08/2012 SUHAB/ PRODAM, PROCESSAMENTOS DE DADOS AMAZONAS SA, REFERENTE A CONTRATAÇÃO DE SERVIÇOS DE LOTAÇÃO DE EQUIPAMENTOS, COMPREENDENDO A INSTALAÇÃO E CONFIG</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2016NE00052</t>
+          <t>2016NE00099</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>1/2015</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>7802.82</v>
+        <v>8413.940000000001</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7463,19 +7463,19 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALDO DO 5º TERMO ADITIVO AO CONTRATO Nº 04/2011 - FEH/SUHAB - PRODAM S.A , REFERENTE AOS SERVIÇOS DE INFORMÁTICA PARA PROCESSAMENTO MENSAL DO SISTEMA CADASTRO E FOLHA DE PAGAMENTO DE PESSOAL - CFPP. </t>
+          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 01/2015 SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE SERVIÇOS DE REDE COMPREENDENDO DISPONIBILIDADE DE ACESSO A REDE DO GOVERNO, VIA CIRCUITO DE</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2016NE00103</t>
+          <t>2016NE00075</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>17/2013</t>
+          <t>14/2014</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>7674.66</v>
+        <v>25581</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -7493,28 +7493,24 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALDO DO 2º TERMO ADITIVO AO CONTRATO Nº 17/2013 SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S.A, REFERENTE A CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DE SISTEMA, COMPREENDENDO GERAÇÃO DE CONSIGNAÇÃO DO </t>
+          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 014/2011- SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS ,REFERENTE A CONTRATAÇÃO DE SERVIÇOS DE SISTEMAS PRODAM-RH, PARA MANTER O CADASTRO DOS SERVIDORES E FOL</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2015NE01187</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>4/2011</t>
-        </is>
-      </c>
+          <t>2015NE01188</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr">
         <is>
           <t>03/11/2015</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>706.03</v>
+        <v>210.89</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7523,14 +7519,14 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>COMPLEMENTO DA FATURA Nº 12623 PRODAM FEH/SUHAB,REFERENTE AO MÊS DE NOVEMBRO/2014.</t>
+          <t>COMPLEMENTO DA FATURA Nº 13008 PRODAM,REFERENTE AO MÊS DE DEZEMBRO/2014.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2015NE01190</t>
+          <t>2015NE01189</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -7540,7 +7536,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>210.89</v>
+        <v>706.03</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7549,14 +7545,14 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE Nº 1188 POR ERRO NO PROGRAMA DE TRABALHO.</t>
+          <t>ANULAÇÃO DA NE Nº 1187 POR ERRO NATUREZA DE DESPESA.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2015NE01191</t>
+          <t>2015NE01186</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7570,7 +7566,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>916.92</v>
+        <v>5116.2</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7579,14 +7575,14 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>COMPLEMENTO DAS FATURAS Nº 12623 E 13008 REFERENTE A SERVIÇOS DE EXECUÇÃO DE SISTEMAS/CADASTRO FOLHA DE PAGAMENTO DE PESSOAL CORRESPONDENTE AOS MESES DE NOVEMBRO E DEZEMBRO/2014 RESPECTIVAMENTE. INFOR</t>
+          <t>1º TERMO ADITIVO</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2015NE01186</t>
+          <t>2015NE01191</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7600,7 +7596,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>5116.2</v>
+        <v>916.92</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7609,14 +7605,14 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>1º TERMO ADITIVO</t>
+          <t>COMPLEMENTO DAS FATURAS Nº 12623 E 13008 REFERENTE A SERVIÇOS DE EXECUÇÃO DE SISTEMAS/CADASTRO FOLHA DE PAGAMENTO DE PESSOAL CORRESPONDENTE AOS MESES DE NOVEMBRO E DEZEMBRO/2014 RESPECTIVAMENTE. INFOR</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2015NE01189</t>
+          <t>2015NE01190</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -7626,7 +7622,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>706.03</v>
+        <v>210.89</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7635,24 +7631,28 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE Nº 1187 POR ERRO NATUREZA DE DESPESA.</t>
+          <t>ANULAÇÃO DA NE Nº 1188 POR ERRO NO PROGRAMA DE TRABALHO.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2015NE01188</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr"/>
+          <t>2015NE01187</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>4/2011</t>
+        </is>
+      </c>
       <c r="C247" t="inlineStr">
         <is>
           <t>03/11/2015</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>210.89</v>
+        <v>706.03</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>COMPLEMENTO DA FATURA Nº 13008 PRODAM,REFERENTE AO MÊS DE DEZEMBRO/2014.</t>
+          <t>COMPLEMENTO DA FATURA Nº 12623 PRODAM FEH/SUHAB,REFERENTE AO MÊS DE NOVEMBRO/2014.</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2015NE00844</t>
+          <t>2015NE00857</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>25/2013</t>
+          <t>17/2013</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>29148.16</v>
+        <v>5481.9</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -7721,19 +7721,19 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>NE 844 DE 03/08/2015 R$ 29.148,16 Referente ao pagamento da última parcela do Contrato 25/2013</t>
+          <t>NE 857 DE 03/08/2015 R$ 5.481,90 2º Termo Aditivo ao Contrato 17/2013 - SUHAB Agosto a Dezembro R$ 1.096,38</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2015NE00857</t>
+          <t>2015NE00844</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>17/2013</t>
+          <t>25/2013</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>5481.9</v>
+        <v>29148.16</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7751,19 +7751,19 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>NE 857 DE 03/08/2015 R$ 5.481,90 2º Termo Aditivo ao Contrato 17/2013 - SUHAB Agosto a Dezembro R$ 1.096,38</t>
+          <t>NE 844 DE 03/08/2015 R$ 29.148,16 Referente ao pagamento da última parcela do Contrato 25/2013</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2024NE0000272</t>
+          <t>2024NE0000270</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>10/2018</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>4452.84</v>
+        <v>3606.6</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7781,19 +7781,19 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2024NE0000276</t>
+          <t>2024NE0000271</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7802,7 +7802,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>14351.31</v>
+        <v>17311.46</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
@@ -7848,12 +7848,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2024NE0000271</t>
+          <t>2024NE0000276</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>17311.46</v>
+        <v>14351.31</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -7871,19 +7871,19 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2024NE0000270</t>
+          <t>2024NE0000272</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>10/2018</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>3606.6</v>
+        <v>4452.84</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -7901,19 +7901,19 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução de Sistema, compreendendo geração de consignações da Financiamento da Casa Própria em folha de pagamento em favor da SUHAB. TC</t>
+          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2020NE00920</t>
+          <t>2020NE00921</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>23/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>8376.440000000001</v>
+        <v>1679.75</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -7931,19 +7931,19 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de execução de Sistemas PRODAM-RH para manter o cadastro dos servidores e folha de pagamento, para atender as necessidades desta SUHAB.</t>
+          <t>Serviços de licença de uso de sistema de informação compreendendo a disponibilidade de Gestor de Conteúdo Web, para publicação de informações, notícias, vídeos e imagens via Website. Mês 04/2020. Pare</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2020NE00921</t>
+          <t>2020NE00920</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>23/2016</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1679.75</v>
+        <v>8376.440000000001</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Serviços de licença de uso de sistema de informação compreendendo a disponibilidade de Gestor de Conteúdo Web, para publicação de informações, notícias, vídeos e imagens via Website. Mês 04/2020. Pare</t>
+          <t>Contratação dos serviços de execução de Sistemas PRODAM-RH para manter o cadastro dos servidores e folha de pagamento, para atender as necessidades desta SUHAB.</t>
         </is>
       </c>
     </row>
@@ -8028,12 +8028,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025NE0000013</t>
+          <t>2025NE0000063</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>4783.77</v>
+        <v>2372.03</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8051,19 +8051,19 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
+          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2025NE0000011</t>
+          <t>2025NE0000015</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>17941.56</v>
+        <v>3606.6</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação de solução tecnológica para gestão de margem consignável em folha de pagamento referente às parcelas de financiamentos da casa própria de servidores ativos, aposentados e pensionistas de Ó</t>
         </is>
       </c>
     </row>
@@ -8118,12 +8118,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2025NE0000015</t>
+          <t>2025NE0000011</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>4/2024</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>3606.6</v>
+        <v>17941.56</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8141,19 +8141,19 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Contratação de solução tecnológica para gestão de margem consignável em folha de pagamento referente às parcelas de financiamentos da casa própria de servidores ativos, aposentados e pensionistas de Ó</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2025NE0000063</t>
+          <t>2025NE0000013</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>2372.03</v>
+        <v>4783.77</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8171,19 +8171,19 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestação de serviço de Licença de Uso de Sistema de Informação, compreendendo a disponibilização de Gestor de Conteúdo Web, para a publicação de informações, notícias, víd</t>
+          <t>Contratação para a prestação de serviços de fornecimento de Execução de Sistemas PRODAM-RH para controle de cadastro de pessoal, processamento de folha de pagamento de servidores para atender às neces</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2024NE0000029</t>
+          <t>2024NE0000047</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>9/2020</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>17311.46</v>
+        <v>8012.7</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
+          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2024NE0000047</t>
+          <t>2024NE0000029</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>9/2020</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>8012.7</v>
+        <v>17311.46</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8261,24 +8261,28 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Contratação da PRODAM para prestação de serviço de Firewall, compreendendo a prestação de serviços de gestão continuada em Segurança de Tecnologia da Informação, com a disponibilização de appliance. T</t>
+          <t>Contratação de empresa especializada na prestação dos serviços de Informática consistindo no fornecimento de Circuito de Transmissão de Dados e Acesso Gerenciado à Rede Mundial, para atender às necess</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2023NE0000006</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr"/>
+          <t>2023NE0000087</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>9/2020</t>
+        </is>
+      </c>
       <c r="C268" t="inlineStr">
         <is>
           <t>02/01/2023</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>2090.14</v>
+        <v>57696.45</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8287,24 +8291,28 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE Nº 005 MOTIVO DATA DE EMISSÃO INCORRETA</t>
+          <t>SALDO DO 2º TERMO ADITIVO AO TERMO AO CONTRATO 009/2020 -SUHAB/PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A, PARA CONTINUIDADE DO SERVIÇO CIRCUITO DE TRANSMISSÃO DE DADOS E ACESSO GERENCIADO A REDE M</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2023NE0000007</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr"/>
+          <t>2023NE0000018</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1/2021</t>
+        </is>
+      </c>
       <c r="C269" t="inlineStr">
         <is>
           <t>02/01/2023</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>28950</v>
+        <v>2090.14</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -8313,19 +8321,19 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALDO DO TERMO DE CONTRATO Nº 007/2022-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A PARA PRESTAÇÃO DE SERVIÇO DE IMPRESSÃO DE DOCUMENTOS E ENVELOPAMENTO DOS BOLETOS DE COBRANÇA DOS FINANCIAMENTOS </t>
+          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 001/2021-SUHAB/PRODAM PROCESSMANTO DE DADOS AMAZONAS S/A, POR PERÍODO DE 12(DOZE) MESES, PARA CONTINUIDADE DOS SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMA</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2023NE0000010</t>
+          <t>2023NE0000014</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>9/2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8334,7 +8342,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>20031.75</v>
+        <v>4490.92</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -8343,7 +8351,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>SALDO DO TERMO DE CONTRATO Nº 009/2022 - SUHAB/PRODAM PROCESSAMENTOS DE DADOS AMAZONAS S/A, PELO PRAZO DE 12(DOZE) MESES, PRESTAÇÃO DE SERVIÇOS DE FIREWALL, COMPREENDENDO A PRESTAÇÃO DE SERVIÇOS DE GE</t>
+          <t>SALDO DO TERMO DE CONTRATO Nº 001/2022-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, POR 12(DOZE) MESES, PARA FORNECIMENTO DE SERVIÇO DE EXECUÇÃO DE SISTEMAS PRODAM-RH PARA CONTROLE DE CADASTRO PE</t>
         </is>
       </c>
     </row>
@@ -8380,12 +8388,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2023NE0000014</t>
+          <t>2023NE0000010</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8394,7 +8402,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>4490.92</v>
+        <v>20031.75</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -8403,28 +8411,24 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>SALDO DO TERMO DE CONTRATO Nº 001/2022-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, POR 12(DOZE) MESES, PARA FORNECIMENTO DE SERVIÇO DE EXECUÇÃO DE SISTEMAS PRODAM-RH PARA CONTROLE DE CADASTRO PE</t>
+          <t>SALDO DO TERMO DE CONTRATO Nº 009/2022 - SUHAB/PRODAM PROCESSAMENTOS DE DADOS AMAZONAS S/A, PELO PRAZO DE 12(DOZE) MESES, PRESTAÇÃO DE SERVIÇOS DE FIREWALL, COMPREENDENDO A PRESTAÇÃO DE SERVIÇOS DE GE</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2023NE0000018</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>1/2021</t>
-        </is>
-      </c>
+          <t>2023NE0000007</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr">
         <is>
           <t>02/01/2023</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>2090.14</v>
+        <v>28950</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -8433,28 +8437,24 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 001/2021-SUHAB/PRODAM PROCESSMANTO DE DADOS AMAZONAS S/A, POR PERÍODO DE 12(DOZE) MESES, PARA CONTINUIDADE DOS SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMA</t>
+          <t xml:space="preserve">SALDO DO TERMO DE CONTRATO Nº 007/2022-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A PARA PRESTAÇÃO DE SERVIÇO DE IMPRESSÃO DE DOCUMENTOS E ENVELOPAMENTO DOS BOLETOS DE COBRANÇA DOS FINANCIAMENTOS </t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2023NE0000087</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>9/2020</t>
-        </is>
-      </c>
+          <t>2023NE0000006</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
         <is>
           <t>02/01/2023</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>57696.45</v>
+        <v>2090.14</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -8463,19 +8463,19 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>SALDO DO 2º TERMO ADITIVO AO TERMO AO CONTRATO 009/2020 -SUHAB/PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A, PARA CONTINUIDADE DO SERVIÇO CIRCUITO DE TRANSMISSÃO DE DADOS E ACESSO GERENCIADO A REDE M</t>
+          <t>ANULAÇÃO DA NE Nº 005 MOTIVO DATA DE EMISSÃO INCORRETA</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2020NE00040</t>
+          <t>2020NE00026</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>17/2016</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>6719</v>
+        <v>319318.17</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -8493,19 +8493,19 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo web para atender as necessidades da Suhab.</t>
+          <t>Contratação para continuidade dos serviços especializados em informática, compreendendo Licença de Uso do Sistema de Informação, Hospedagem de Sistemas, Data Center, impressão de documentos, envelopam</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2020NE00027</t>
+          <t>2020NE00023</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>10/2018</t>
+          <t>1/2015</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>11360</v>
+        <v>10314.28</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -8523,19 +8523,19 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de serviços de execução de sistema, compreendendo geração de consignações do FINANCIAMENTO DA CASA PRÓPRIA, em folha de pagamento em favor da SUHAB.</t>
+          <t>Contratação dos serviços de rede, compreendendo a disponibilidade de acesso à rede de governo, via circuito de transmissão de dados dedicado entre a Suhab e Prodam.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2020NE00028</t>
+          <t>2020NE00024</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>23/2016</t>
+          <t>28/2017</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>45994.92</v>
+        <v>32669.6</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -8553,19 +8553,19 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada na prestação de Serviços de Execução de Sistema PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de pessoal, processar folhas de pagamento e f</t>
+          <t>Contratação de serviços de Firewall, compreendendo a prestação de serviços de gestão continuidade em Segurança de Tecnologia da Informação, com a disponibilidade de appliance (conjunto de equipamentos</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2020NE00024</t>
+          <t>2020NE00028</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>28/2017</t>
+          <t>23/2016</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>32669.6</v>
+        <v>45994.92</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -8583,19 +8583,19 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Contratação de serviços de Firewall, compreendendo a prestação de serviços de gestão continuidade em Segurança de Tecnologia da Informação, com a disponibilidade de appliance (conjunto de equipamentos</t>
+          <t>Contratação de empresa especializada na prestação de Serviços de Execução de Sistema PRODAM-RH, para manter o cadastro dos servidores e Folha de Pagamento de pessoal, processar folhas de pagamento e f</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2020NE00023</t>
+          <t>2020NE00027</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>1/2015</t>
+          <t>10/2018</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>10314.28</v>
+        <v>11360</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -8613,19 +8613,19 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de rede, compreendendo a disponibilidade de acesso à rede de governo, via circuito de transmissão de dados dedicado entre a Suhab e Prodam.</t>
+          <t>Contratação de empresa especializada na prestação de serviços de execução de sistema, compreendendo geração de consignações do FINANCIAMENTO DA CASA PRÓPRIA, em folha de pagamento em favor da SUHAB.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2020NE00026</t>
+          <t>2020NE00040</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>17/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>319318.17</v>
+        <v>6719</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -8643,19 +8643,19 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Contratação para continuidade dos serviços especializados em informática, compreendendo Licença de Uso do Sistema de Informação, Hospedagem de Sistemas, Data Center, impressão de documentos, envelopam</t>
+          <t>Contratação dos serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo web para atender as necessidades da Suhab.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2019NE00031</t>
+          <t>2019NE00050</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>23/2016</t>
+          <t>17/2016</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>43224.3</v>
+        <v>327620.46</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -8673,19 +8673,19 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Contratação de empresa para prestaçãode serviços de sistema PRODAM-RH, para manter o cadstro dps servidores e folha de pagamentode pessoal, processar folhas de pagamento e fornecer relatórios para ate</t>
+          <t>Contratação dos serviços de execução de sistema em plataforma web (Sproweb), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do cliente: Para atender as necessi</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2019NE00028</t>
+          <t>2019NE00037</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>28/2017</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>31217.92</v>
+        <v>6294.16</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -8703,19 +8703,19 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação dos serviços de fireqall, compreendendo a prestação de serviços de gestão continuada em segurança de tecnologia da informação, com disponibilidade de appliance (conjunto de equipamentos e </t>
+          <t>Contratação dos serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo ueb,para publicação de informações, notícias,vídeos e imagens via website pa</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2019NE00032</t>
+          <t>2019NE00041</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>1/2015</t>
+          <t>10/2018</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>10024.1</v>
+        <v>11360</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -8733,19 +8733,19 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de rede, compreendendo a disponibilidade de acesso a rede do Governo, via circuito de transmissão de dados dedicado entre a SUHAB e Prodam de interesse desta SUHAB.</t>
+          <t>Contratação dos serviços de execução de sistema , compreendendo geração de consignações do "financiamento da casa própria" em folha de pagamento em favor da Suhab.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2019NE00041</t>
+          <t>2019NE00032</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>10/2018</t>
+          <t>1/2015</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>11360</v>
+        <v>10024.1</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -8763,19 +8763,19 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de execução de sistema , compreendendo geração de consignações do "financiamento da casa própria" em folha de pagamento em favor da Suhab.</t>
+          <t>Contratação dos serviços de rede, compreendendo a disponibilidade de acesso a rede do Governo, via circuito de transmissão de dados dedicado entre a SUHAB e Prodam de interesse desta SUHAB.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2019NE00037</t>
+          <t>2019NE00028</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>28/2017</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>6294.16</v>
+        <v>31217.92</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8793,19 +8793,19 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo ueb,para publicação de informações, notícias,vídeos e imagens via website pa</t>
+          <t xml:space="preserve">Contratação dos serviços de fireqall, compreendendo a prestação de serviços de gestão continuada em segurança de tecnologia da informação, com disponibilidade de appliance (conjunto de equipamentos e </t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2019NE00050</t>
+          <t>2019NE00031</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>17/2016</t>
+          <t>23/2016</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8814,7 +8814,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>327620.46</v>
+        <v>43224.3</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -8823,19 +8823,19 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de execução de sistema em plataforma web (Sproweb), objetivando o controle e acompanhamento do registro de todos os documentos ou processos do cliente: Para atender as necessi</t>
+          <t>Contratação de empresa para prestaçãode serviços de sistema PRODAM-RH, para manter o cadstro dps servidores e folha de pagamentode pessoal, processar folhas de pagamento e fornecer relatórios para ate</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2018NE00064</t>
+          <t>2018NE00062</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>28/2017</t>
+          <t>17/2013</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>32123.47</v>
+        <v>8812.23</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -8853,19 +8853,19 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO Nº 028/2017-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE A CONTRATAÇÃO DOS SERVIÇOS DE FIREWALL, COMPREENDENDO A PRESTAÇÃO DE SERVIÇOS DE GESTÃO CONTINUADA EM SEGURANÇ</t>
+          <t xml:space="preserve">CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DE SISTEMA COMPREENDENDO GERAÇÃO DE CONSIGNAÇÃO DO "FINANCIAMENTO DA CASA PRÓPRIA" EM FOLHA DE PAGAMENTO EM FAVOR DA SUHAB, CUJA A DESCRIÇÃO ESTÁ CONTIDA NO ANEXO </t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2018NE00058</t>
+          <t>2018NE00047</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>17/2016</t>
+          <t>1/2015</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>273017.05</v>
+        <v>10024.1</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -8883,19 +8883,19 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 017/2016- PRORROGAÇÃO DE PRAZO CONTRATUAL E REAJUSTE NO PERCENTUAL 4,86%,COM BASE NO IGPM ACUMULADO DO PERÍODO,PRODAM/SUHAB-PROCESSAMENTO DE DADOS AMAZONAS S/A</t>
+          <t>SALDO DO 3º TERMO ADITIVO AO TERMO DE CONTRATO 001/2015-SUHAB,REFERENTE A PRORROGAÇÃO DO PRAZO PELO PERÍODO DE 12(DOZE)MESES E REJUSTE COM BASE IGPM NO PERCENTUAL DE 8,79%,CORRESPONDENTE A CONTRATAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2018NE00035</t>
+          <t>2018NE00033</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>23/2016</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>6294.21</v>
+        <v>39688.08</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -8913,19 +8913,19 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DOS SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEOS E IMAGENS VIA WEBSITE.</t>
+          <t xml:space="preserve">1º TERMO ADITIVO AO CONTRATO Nº 023/2016-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, PELO PERÍODO DE 12 (DOZE) MESES, PARA CONTINUIDADE DOS SERVIÇOS DE INFORMÁTICA, REFERENTE A PROCESSAMENTO DE </t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2018NE00033</t>
+          <t>2018NE00035</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>23/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>39688.08</v>
+        <v>6294.21</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -8943,19 +8943,19 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">1º TERMO ADITIVO AO CONTRATO Nº 023/2016-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, PELO PERÍODO DE 12 (DOZE) MESES, PARA CONTINUIDADE DOS SERVIÇOS DE INFORMÁTICA, REFERENTE A PROCESSAMENTO DE </t>
+          <t>CONTRATAÇÃO DOS SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTÍCIAS, VÍDEOS E IMAGENS VIA WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2018NE00047</t>
+          <t>2018NE00058</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>1/2015</t>
+          <t>17/2016</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>10024.1</v>
+        <v>273017.05</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -8973,19 +8973,19 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>SALDO DO 3º TERMO ADITIVO AO TERMO DE CONTRATO 001/2015-SUHAB,REFERENTE A PRORROGAÇÃO DO PRAZO PELO PERÍODO DE 12(DOZE)MESES E REJUSTE COM BASE IGPM NO PERCENTUAL DE 8,79%,CORRESPONDENTE A CONTRATAÇÃO</t>
+          <t>SALDO DO 1º TERMO ADITIVO AO CONTRATO Nº 017/2016- PRORROGAÇÃO DE PRAZO CONTRATUAL E REAJUSTE NO PERCENTUAL 4,86%,COM BASE NO IGPM ACUMULADO DO PERÍODO,PRODAM/SUHAB-PROCESSAMENTO DE DADOS AMAZONAS S/A</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2018NE00062</t>
+          <t>2018NE00064</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>17/2013</t>
+          <t>28/2017</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>8812.23</v>
+        <v>32123.47</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -9003,19 +9003,19 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRATAÇÃO DOS SERVIÇOS DE EXECUÇÃO DE SISTEMA COMPREENDENDO GERAÇÃO DE CONSIGNAÇÃO DO "FINANCIAMENTO DA CASA PRÓPRIA" EM FOLHA DE PAGAMENTO EM FAVOR DA SUHAB, CUJA A DESCRIÇÃO ESTÁ CONTIDA NO ANEXO </t>
+          <t>TERMO DE CONTRATO Nº 028/2017-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE A CONTRATAÇÃO DOS SERVIÇOS DE FIREWALL, COMPREENDENDO A PRESTAÇÃO DE SERVIÇOS DE GESTÃO CONTINUADA EM SEGURANÇ</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2017NE00016</t>
+          <t>2017NE00009</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>1/2015</t>
+          <t>23/2016</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>9214.17</v>
+        <v>39688.08</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9033,19 +9033,19 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>SALDO 2º TERMO ADITIVO AO CONTRATO 001/2015 SUHAB/ PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A, REFERENTE A CONTRATAÇÃO DOS SERVIÇOS DE REDE, COMPREENDENDO A DISPONIBILIDADE DE ACESSO A REDE DO GOVE</t>
+          <t>Contratação dos serviços de processamento de cadastro de folha de pagamento pessoal-Sistema CFPP, para manter o cadastro dos servidores e folha pagamento de pessoal, processar folhas de pagamento e fo</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2017NE00018</t>
+          <t>2017NE00027</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>17/2016</t>
+          <t>17/2013</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9054,7 +9054,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>347538.7</v>
+        <v>8525.77</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9063,19 +9063,19 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>SALDO TERMO DE CONTRATO Nº 017/2016-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA, COMPREENDENDO A EXECUÇÃO DE SISTEMA EM PLATAFORMA WEB (SPROweb),</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA COMPREENDENDO GERAÇÃO DE CONSIGNAÇÕES DO FINANCIAMENTO DA CASA PRÓPRIA EM FOLHA DE PAGAMENTO EM FAVOR DA SUHAB.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2017NE00017</t>
+          <t>2017NE00008</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>8/2012</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>32739.44</v>
+        <v>5901.16</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -9093,19 +9093,19 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE LOCAÇÃO DE EQUIPAMENTOS, COMPREENDENDO A INSTALAÇÃO E CONFIGURAÇÃO DE UM FIREWALL UTM TIPO 6 PARA ATÉ 250 USUÁRIOS.</t>
+          <t>TERMO DE CONTRATO Nº 10/2016-SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS SA .CONTRATAÇÃO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO,COMPREENDENDO A DISPONIBILIDADE DE GESTOR DE CONTEÚDO WEB A ESSA S</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2017NE00008</t>
+          <t>2017NE00017</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>8/2012</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>5901.16</v>
+        <v>32739.44</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -9123,19 +9123,19 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO Nº 10/2016-SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS SA .CONTRATAÇÃO DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO,COMPREENDENDO A DISPONIBILIDADE DE GESTOR DE CONTEÚDO WEB A ESSA S</t>
+          <t>CONTRATAÇÃO DE SERVIÇOS DE LOCAÇÃO DE EQUIPAMENTOS, COMPREENDENDO A INSTALAÇÃO E CONFIGURAÇÃO DE UM FIREWALL UTM TIPO 6 PARA ATÉ 250 USUÁRIOS.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2017NE00027</t>
+          <t>2017NE00018</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>17/2013</t>
+          <t>17/2016</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>8525.77</v>
+        <v>347538.7</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9153,19 +9153,19 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA COMPREENDENDO GERAÇÃO DE CONSIGNAÇÕES DO FINANCIAMENTO DA CASA PRÓPRIA EM FOLHA DE PAGAMENTO EM FAVOR DA SUHAB.</t>
+          <t>SALDO TERMO DE CONTRATO Nº 017/2016-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, REFERENTE SERVIÇOS ESPECIALIZADOS EM INFORMÁTICA, COMPREENDENDO A EXECUÇÃO DE SISTEMA EM PLATAFORMA WEB (SPROweb),</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2017NE00009</t>
+          <t>2017NE00016</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>23/2016</t>
+          <t>1/2015</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>39688.08</v>
+        <v>9214.17</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9183,19 +9183,19 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Contratação dos serviços de processamento de cadastro de folha de pagamento pessoal-Sistema CFPP, para manter o cadastro dos servidores e folha pagamento de pessoal, processar folhas de pagamento e fo</t>
+          <t>SALDO 2º TERMO ADITIVO AO CONTRATO 001/2015 SUHAB/ PRODAM PROCESSAMENTO DE DADOS DA AMAZONAS S/A, REFERENTE A CONTRATAÇÃO DOS SERVIÇOS DE REDE, COMPREENDENDO A DISPONIBILIDADE DE ACESSO A REDE DO GOVE</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2014NE00047</t>
+          <t>2014NE00048</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>13/2009</t>
+          <t>17/2013</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>73980.36</v>
+        <v>7000</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -9213,19 +9213,19 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Contrato No. 13/2009 - Acesso Computador Central 3 Mbps /Internet link 2 Mbps</t>
+          <t>Contrato No. 17/2013 - Execução Sistema Financiamento da Casa Própria</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2014NE00049</t>
+          <t>2014NE00073</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>7/2009</t>
+          <t>25/2013</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>259479.71</v>
+        <v>174888.99</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Contrato No. 7/2009 - CFPP, SGH2000-Imobiliario</t>
+          <t>Contrato No. 25/2013 - Instalação de Redes elétricas e lógicas - 458 pontos telec. 229 elé‚tricos</t>
         </is>
       </c>
     </row>
@@ -9280,12 +9280,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2014NE00073</t>
+          <t>2014NE00049</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>25/2013</t>
+          <t>7/2009</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>174888.99</v>
+        <v>259479.71</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -9303,19 +9303,19 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Contrato No. 25/2013 - Instalação de Redes elétricas e lógicas - 458 pontos telec. 229 elé‚tricos</t>
+          <t>Contrato No. 7/2009 - CFPP, SGH2000-Imobiliario</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2014NE00048</t>
+          <t>2014NE00047</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>17/2013</t>
+          <t>13/2009</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>7000</v>
+        <v>73980.36</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -9333,14 +9333,14 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Contrato No. 17/2013 - Execução Sistema Financiamento da Casa Própria</t>
+          <t>Contrato No. 13/2009 - Acesso Computador Central 3 Mbps /Internet link 2 Mbps</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2022NE0000535</t>
+          <t>2022NE00535</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9363,14 +9363,14 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO Nº 009/2022 - SUHAB/PRODAM PROCESSAMENTOS DE DADOS AMAZONAS S/A, PELO PRAZO DE 12(DOZE) MESES, PRESTAÇÃO DE SERVIÇOS DE FIREWALL, COMPREENDENDO A PRESTAÇÃO DE SERVIÇOS DE GESTÃO CONT</t>
+          <t>Serviço de Firewall contrato 009/2022</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2022NE00535</t>
+          <t>2022NE0000535</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Serviço de Firewall contrato 009/2022</t>
+          <t>TERMO DE CONTRATO Nº 009/2022 - SUHAB/PRODAM PROCESSAMENTOS DE DADOS AMAZONAS S/A, PELO PRAZO DE 12(DOZE) MESES, PRESTAÇÃO DE SERVIÇOS DE FIREWALL, COMPREENDENDO A PRESTAÇÃO DE SERVIÇOS DE GESTÃO CONT</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2015NE00380</t>
+          <t>2015NE00396</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -9569,19 +9569,19 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>TERMO DE CONTRATO Nº 01/2015 SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A REFERENTE SERVIÇOS DE REDE, COMPREENDENDO DISPONIBILIDADE DE ACESSO À REDE DO GOVERNO, VIA CIRCUITO DE TRANSMISSÃO DE DAD</t>
+          <t>ANULAÇÃO DA NE Nº 380 POR ERRO NA DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2015NE00406</t>
+          <t>2015NE00398</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>1/2015</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>10403.76</v>
+        <v>75725.46000000001</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -9599,19 +9599,19 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Alteração da dotação orçamentária da FEH para SUHAB</t>
+          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2015NE00398</t>
+          <t>2015NE00406</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>1/2015</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>75725.46000000001</v>
+        <v>10403.76</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -9629,14 +9629,14 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE PROCESSAMENTO DE DADOS</t>
+          <t>Alteração da dotação orçamentária da FEH para SUHAB</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2015NE00396</t>
+          <t>2015NE00380</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE Nº 380 POR ERRO NA DESCRIÇÃO.</t>
+          <t>TERMO DE CONTRATO Nº 01/2015 SUHAB/ PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A REFERENTE SERVIÇOS DE REDE, COMPREENDENDO DISPONIBILIDADE DE ACESSO À REDE DO GOVERNO, VIA CIRCUITO DE TRANSMISSÃO DE DAD</t>
         </is>
       </c>
     </row>
@@ -9696,12 +9696,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2023NE00094</t>
+          <t>2023NE0000093</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>4783.77</v>
+        <v>2226.42</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -9719,19 +9719,19 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>2º TERMO ADITIVO AO CONTRATO Nº 001/2021-SUHAB/PRODAM PROCESSMANTO DE DADOS AMAZONAS S/A, POR PERIODO DE 12(DOZE) MESES, PARA CONTINUIDADE DOS SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO COMPR</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2023NE00093</t>
+          <t>2023NE0000094</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9740,7 +9740,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>2226.42</v>
+        <v>4783.77</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -9749,19 +9749,19 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t xml:space="preserve">1º TERMO ADITIVO AO CONTRATO Nº 001/2022-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, POR 12(DOZE) MESES, PARA FORNECIMENTO DE SERVIÇO DE EXECUÇÃO DE SISTEMAS PRODAM-RH PARA CONTROLE DE CADASTRO </t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2023NE0000094</t>
+          <t>2023NE00093</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>1/2022</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>4783.77</v>
+        <v>2226.42</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -9779,19 +9779,19 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">1º TERMO ADITIVO AO CONTRATO Nº 001/2022-SUHAB/PRODAM PROCESSAMENTO DE DADOS AMAZONAS S/A, POR 12(DOZE) MESES, PARA FORNECIMENTO DE SERVIÇO DE EXECUÇÃO DE SISTEMAS PRODAM-RH PARA CONTROLE DE CADASTRO </t>
+          <t>Cobertura Financeira</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2023NE0000093</t>
+          <t>2023NE00094</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>2226.42</v>
+        <v>4783.77</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>2º TERMO ADITIVO AO CONTRATO Nº 001/2021-SUHAB/PRODAM PROCESSMANTO DE DADOS AMAZONAS S/A, POR PERIODO DE 12(DOZE) MESES, PARA CONTINUIDADE DOS SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMAÇÃO COMPR</t>
+          <t>Cobertura Financeira</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/SUHAB/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SUHAB/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
